--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.11.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.11.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.11.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.11.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="39" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="39" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.11.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.11.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0011.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0011.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -595,22 +595,26 @@
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>L1: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): TUyLL (odd internal casing) :: LETARGE vs.DE TUyLLâ€”Grant's Chancery Reports, Vol.1,p.227;</t>
+          <t>L1: suspicious token(s): TUyLL (odd internal casing) :: LETARGE vs.DE TUyLL—Grant's Chancery Reports, Vol.1,p.227;</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L1: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): TUyLL (odd internal casing) :: LETARGE vs.DE TUyLLâ€”Grant's Chancery Reports, Vol.1,p.227;</t>
+          <t>L63: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L7: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+2122 TRADE MARK SIGN :: â€¢ LETARGE vs. DE Tuyll,â€”Grantâ€™s Chancery Reports,Vol. 1, p. 227 ;</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]by</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]by</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L19: isolated marker/symbol line :: T</t>
@@ -624,7 +628,11 @@
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L7: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • LETARGE vs. DE Tuyll,—Grant’s Chancery Reports,Vol. 1, p. 227 ;</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -645,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -660,12 +668,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L30: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): HoRToN (odd internal casing) :: the reader is referred to STUART, vs. HoRToN,â€” Grant's Chancery</t>
+          <t>L64: stray/suspicious non-ASCII glyph(s): U+540A CJK UNIFIED IDEOGRAPH-540A | isolated marker/symbol line :: 吊</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L11: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: words of the conveyanceâ€”in short, where the Statute of Frauds</t>
+          <t>L7: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • LETARGE vs. DE Tuyll,—Grant’s Chancery Reports,Vol. 1, p. 227 ;</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -717,16 +725,8 @@
         </is>
       </c>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L61: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: BRENNAN,â€”Grant's Chancery Reports, Vol.1, p.371.</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: the reader is referred to STUART, VS. HORTON,â€”Grant's Chancery</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -772,21 +772,13 @@
         </is>
       </c>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L64: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: å�Š</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L43: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: BRENNAN,â€”Grantâ€™s Chancery Reports, Vol.1, p. 371.</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: I</t>
+          <t>L63: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr"/>
@@ -823,7 +815,7 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>L30: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): HoRToN (odd internal casing) :: the reader is referred to STUART, vs. HoRToN,â€” Grant's Chancery</t>
+          <t>L30: suspicious token(s): HoRToN (odd internal casing) :: the reader is referred to STUART, vs. HoRToN,— Grant's Chancery</t>
         </is>
       </c>
       <c r="I6" s="1" t="inlineStr"/>
@@ -833,7 +825,7 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L71: isolated marker/symbol line :: 4</t>
+          <t>L64: stray/suspicious non-ASCII glyph(s): U+540A CJK UNIFIED IDEOGRAPH-540A | isolated marker/symbol line :: 吊</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr"/>
@@ -878,7 +870,11 @@
       <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
-      <c r="N7" s="1" t="inlineStr"/>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>L67: isolated marker/symbol line :: I</t>
+        </is>
+      </c>
       <c r="O7" s="1" t="inlineStr"/>
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr"/>
@@ -917,7 +913,11 @@
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
-      <c r="N8" s="1" t="inlineStr"/>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>L71: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
       <c r="O8" s="1" t="inlineStr"/>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr"/>
@@ -977,12 +977,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
